--- a/survey_templates/048_wedding_artist_fee_survey--survey_templates.xlsx
+++ b/survey_templates/048_wedding_artist_fee_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,35 +520,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>base_formation</t>
+          <t>artist_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Base Formation</t>
+          <t>Artist Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>travel_preferences</t>
+          <t>base_formation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Travel Preferences</t>
+          <t>Base Formation</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>booking_priorities</t>
+          <t>travel_preferences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Booking Priorities</t>
+          <t>Travel Preferences</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fee_range_3</t>
+          <t>travel_cost_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fee Range 3</t>
+          <t>Travel Cost 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>travel_cost_1</t>
+          <t>travel_cost_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Travel Cost 1</t>
+          <t>Travel Cost 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,23 +676,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>travel_cost_2</t>
+          <t>booking_priorities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travel Cost 2</t>
+          <t>Booking Priorities</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>travel_cost_3</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travel Cost 3</t>
+          <t>Contact Info</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>travel_cost_4</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travel Cost 4</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>base_formation_2</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Base Formation 2</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,115 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>travel_preferences_2</t>
+          <t>service_type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Travel Preferences 2</t>
+          <t>Service Type</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>booking_priorities_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Booking Priorities 2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>fee_range_2_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Fee Range 2</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>fee_range_3_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Fee Range 3</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>travel_cost_3_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Travel Cost 3</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -891,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1021,102 +929,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>travel_preferences_2_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>drive-in</t>
+          <t>photography</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Drive-in</t>
+          <t>Photography</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>travel_preferences_2_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fly</t>
+          <t>hair_and_makeup</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fly</t>
+          <t>Hair and Makeup</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>travel_preferences_2_choices</t>
+          <t>service_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>videography</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>booking_priorities_2_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>budget-friendly</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Budget-friendly</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>booking_priorities_2_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>convenience</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Convenience</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>booking_priorities_2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>time-sensitive</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Time-sensitive</t>
+          <t>Videography</t>
         </is>
       </c>
     </row>
